--- a/output/filtered_scenarios.xlsx
+++ b/output/filtered_scenarios.xlsx
@@ -7,17 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="color codes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="all_scenarios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="green-green" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="green-yellow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="green-red" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="yellow-green" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="yellow-yellow" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="yellow-red" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="red-green" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="red-yellow" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="red-red" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Supp 1 CT usually-Alt usually" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Supp 2 CT usually-Alt may be" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Supp 3 CT usually-Alt not" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Supp 4 CT may be-Alt usually" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Supp 5 CT may be-Alt may be" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Supp 6 CT may be-Alt not" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Supp 7 CT not-Alt usually" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Supp 8 CT not-Alt may be" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Supp 9 CT not-Alt not" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -143,7 +143,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4962525" cy="4676775"/>
+    <ext cx="5057775" cy="4772025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
